--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Foundation_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Foundation_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rba016674445742d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rfb151833506e4338"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R4f522593691844c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rc8970e3f209b41c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R5acea21691844997"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R7f7b7a5f7004402b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R2aba6ec1b8cf4fe6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R3ac71aa56f2a4b8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R4ea71bc5f38049e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R825e34328b094d92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rae32ebd50a464d34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R9d1ef8d940874f9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R522edf57e43741c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R4904ee40bd344fd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Raff3f8c6c88d41f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rce31e380819f4d56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rf913850f1faa420e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R1dd4c5ab52e44d3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Ra4e0bce0778f45f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R830f3c3b9c7c4fd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rc2f2c8ba26964b41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R7c60549d7e774a8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Re46938c0991747fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R37b3fb18098542c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R0178a791364c4663"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rfe1dbbe7fb3640b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Racbf6838c6754007"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R6e3e6580a0094249"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rc136dcc32e5846b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rf529302c862e45cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R222d8bc9bddb4bc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R07d0a0f0cdfc4130"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R32d9b303e2c9472b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R69f9c0b8db594a4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rc6018a7b23bf4c4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R3b2282aab6e244c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R7cc33257bdd04e79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R6603a0c4a6c14d9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Ra115de8061fc489d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rf5815d9f848144bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R4e9bdb83cd504e1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R71a4591ffbb843b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R56307755e3ab4858"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R253b067b437a4f97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Raae072b9431841c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rbba4400e35c34b3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R61feb57f92d64b75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R6fc1428ccf784785"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R05d19e3244a744ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rca387d016ee044b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R6ffe11a9617b4963"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rfa447d7e703542f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R7e224c8485ad4564"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R77e2252939754191"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rba1b0066d3834166"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Ra1f8e35852dc4c85"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -230,12 +230,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -2156,7 +2150,7 @@
       <x:c r="A5" s="2" t="str">
         <x:v>Fiches suivies</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>249</x:v>
       </x:c>
@@ -2164,7 +2158,7 @@
       <x:c r="D5" s="2" t="str">
         <x:v>Intégrés</x:v>
       </x:c>
-      <x:c r="E5" s="33" t="n">
+      <x:c r="E5" s="31" t="n">
         <x:f>SUM(E10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2172,7 +2166,7 @@
       <x:c r="G5" s="2" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="H5" s="33" t="n">
+      <x:c r="H5" s="31" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>28</x:v>
       </x:c>
@@ -2180,7 +2174,7 @@
       <x:c r="J5" s="2" t="str">
         <x:v>Extrapolations</x:v>
       </x:c>
-      <x:c r="K5" s="33" t="n">
+      <x:c r="K5" s="31" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>202</x:v>
       </x:c>
@@ -2203,7 +2197,7 @@
       <x:c r="M6" s="2"/>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="34" t="str">
+      <x:c r="A7" s="32" t="str">
         <x:v>Défini = spécification. Établi = référence documentée. Les colonnes d’adaptation restent des propositions.</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
@@ -2235,95 +2229,95 @@
       <x:c r="M8" s="2"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="30" t="str">
+      <x:c r="A9" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="29" t="str">
         <x:v>Total</x:v>
       </x:c>
-      <x:c r="C9" s="31" t="str">
-        <x:v>Défini</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="str">
+      <x:c r="C9" s="29" t="str">
+        <x:v>Défini</x:v>
+      </x:c>
+      <x:c r="D9" s="29" t="str">
         <x:v>Prototype</x:v>
       </x:c>
-      <x:c r="E9" s="31" t="str">
+      <x:c r="E9" s="29" t="str">
         <x:v>Intégré</x:v>
       </x:c>
-      <x:c r="F9" s="31" t="str">
+      <x:c r="F9" s="29" t="str">
         <x:v>Validé</x:v>
       </x:c>
-      <x:c r="G9" s="31" t="str">
+      <x:c r="G9" s="29" t="str">
         <x:v>Établi</x:v>
       </x:c>
-      <x:c r="H9" s="31" t="str">
+      <x:c r="H9" s="29" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="I9" s="31" t="str">
+      <x:c r="I9" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="str">
+      <x:c r="J9" s="29" t="str">
         <x:v>Coupé attesté</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="str">
+      <x:c r="K9" s="29" t="str">
         <x:v>Concept abandonné</x:v>
       </x:c>
-      <x:c r="L9" s="31" t="str">
+      <x:c r="L9" s="29" t="str">
         <x:v>Allégation écartée</x:v>
       </x:c>
-      <x:c r="M9" s="32" t="str">
+      <x:c r="M9" s="30" t="str">
         <x:v>Priorité P0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="35" t="str">
+      <x:c r="A10" s="33" t="str">
         <x:v>Personnages</x:v>
       </x:c>
-      <x:c r="B10" s="39" t="n">
+      <x:c r="B10" s="37" t="n">
         <x:f>COUNTA('Personnages'!$A$7:$A$17)</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C10" s="39" t="n">
+      <x:c r="C10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$17,"Défini")</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D10" s="39" t="n">
+      <x:c r="D10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$17,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="39" t="n">
+      <x:c r="E10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$17,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="39" t="n">
+      <x:c r="F10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$17,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="39" t="n">
+      <x:c r="G10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$17,"Établi")</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="H10" s="39" t="n">
+      <x:c r="H10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$17,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I10" s="39" t="n">
+      <x:c r="I10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$17,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="J10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$17,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="39" t="n">
+      <x:c r="K10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$17,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="39" t="n">
+      <x:c r="L10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$17,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="n">
+      <x:c r="M10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$E$7:$E$17,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2332,104 +2326,104 @@
       <x:c r="A11" s="2" t="str">
         <x:v>PNJ</x:v>
       </x:c>
-      <x:c r="B11" s="40" t="n">
+      <x:c r="B11" s="38" t="n">
         <x:f>COUNTA('PNJ'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C11" s="40" t="n">
+      <x:c r="C11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D11" s="40" t="n">
+      <x:c r="D11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="40" t="n">
+      <x:c r="E11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F11" s="40" t="n">
+      <x:c r="F11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G11" s="40" t="n">
+      <x:c r="G11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H11" s="40" t="n">
+      <x:c r="H11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I11" s="40" t="n">
+      <x:c r="I11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="40" t="n">
+      <x:c r="K11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L11" s="40" t="n">
+      <x:c r="L11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M11" s="40" t="n">
+      <x:c r="M11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$E$7:$E$13,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="35" t="str">
+      <x:c r="A12" s="33" t="str">
         <x:v>Espèces et factions</x:v>
       </x:c>
-      <x:c r="B12" s="39" t="n">
+      <x:c r="B12" s="37" t="n">
         <x:f>COUNTA('Especes_factions'!$A$7:$A$25)</x:f>
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C12" s="39" t="n">
+      <x:c r="C12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$25,"Défini")</x:f>
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D12" s="39" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$25,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$25,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="39" t="n">
+      <x:c r="F12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$25,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="39" t="n">
+      <x:c r="G12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$25,"Établi")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H12" s="39" t="n">
+      <x:c r="H12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$25,"À vérifier")</x:f>
         <x:v>14</x:v>
       </x:c>
-      <x:c r="I12" s="39" t="n">
+      <x:c r="I12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$25,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="39" t="n">
+      <x:c r="J12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$25,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="39" t="n">
+      <x:c r="K12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$25,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="39" t="n">
+      <x:c r="L12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$25,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="n">
+      <x:c r="M12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$E$7:$E$25,"P0")</x:f>
         <x:v>6</x:v>
       </x:c>
@@ -2438,104 +2432,104 @@
       <x:c r="A13" s="2" t="str">
         <x:v>Mondes</x:v>
       </x:c>
-      <x:c r="B13" s="40" t="n">
+      <x:c r="B13" s="38" t="n">
         <x:f>COUNTA('Mondes'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C13" s="40" t="n">
+      <x:c r="C13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D13" s="40" t="n">
+      <x:c r="D13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E13" s="40" t="n">
+      <x:c r="E13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="40" t="n">
+      <x:c r="F13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="40" t="n">
+      <x:c r="G13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$13,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H13" s="40" t="n">
+      <x:c r="H13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I13" s="40" t="n">
+      <x:c r="I13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J13" s="40" t="n">
+      <x:c r="J13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="40" t="n">
+      <x:c r="K13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L13" s="40" t="n">
+      <x:c r="L13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="40" t="n">
+      <x:c r="M13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$E$7:$E$13,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="35" t="str">
+      <x:c r="A14" s="33" t="str">
         <x:v>Zones</x:v>
       </x:c>
-      <x:c r="B14" s="39" t="n">
+      <x:c r="B14" s="37" t="n">
         <x:f>COUNTA('Zones'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C14" s="39" t="n">
+      <x:c r="C14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D14" s="39" t="n">
+      <x:c r="D14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="39" t="n">
+      <x:c r="E14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="39" t="n">
+      <x:c r="F14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="39" t="n">
+      <x:c r="G14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$13,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H14" s="39" t="n">
+      <x:c r="H14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I14" s="39" t="n">
+      <x:c r="I14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="J14" s="39" t="n">
+      <x:c r="J14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="39" t="n">
+      <x:c r="K14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="39" t="n">
+      <x:c r="L14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="39" t="n">
+      <x:c r="M14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$E$7:$E$13,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2544,104 +2538,104 @@
       <x:c r="A15" s="2" t="str">
         <x:v>Liaisons</x:v>
       </x:c>
-      <x:c r="B15" s="40" t="n">
+      <x:c r="B15" s="38" t="n">
         <x:f>COUNTA('Liaisons'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C15" s="40" t="n">
+      <x:c r="C15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D15" s="40" t="n">
+      <x:c r="D15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="40" t="n">
+      <x:c r="E15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="40" t="n">
+      <x:c r="F15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="40" t="n">
+      <x:c r="G15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$13,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H15" s="40" t="n">
+      <x:c r="H15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I15" s="40" t="n">
+      <x:c r="I15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="J15" s="40" t="n">
+      <x:c r="J15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="40" t="n">
+      <x:c r="K15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="40" t="n">
+      <x:c r="L15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M15" s="40" t="n">
+      <x:c r="M15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$E$7:$E$13,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="35" t="str">
+      <x:c r="A16" s="33" t="str">
         <x:v>Décors</x:v>
       </x:c>
-      <x:c r="B16" s="39" t="n">
+      <x:c r="B16" s="37" t="n">
         <x:f>COUNTA('Decors'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C16" s="39" t="n">
+      <x:c r="C16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D16" s="39" t="n">
+      <x:c r="D16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="39" t="n">
+      <x:c r="E16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="39" t="n">
+      <x:c r="F16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="39" t="n">
+      <x:c r="G16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$13,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H16" s="39" t="n">
+      <x:c r="H16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I16" s="39" t="n">
+      <x:c r="I16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="J16" s="39" t="n">
+      <x:c r="J16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K16" s="39" t="n">
+      <x:c r="K16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L16" s="39" t="n">
+      <x:c r="L16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M16" s="39" t="n">
+      <x:c r="M16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$E$7:$E$13,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2650,104 +2644,104 @@
       <x:c r="A17" s="2" t="str">
         <x:v>Props</x:v>
       </x:c>
-      <x:c r="B17" s="40" t="n">
+      <x:c r="B17" s="38" t="n">
         <x:f>COUNTA('Props'!$A$7:$A$19)</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C17" s="40" t="n">
+      <x:c r="C17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$19,"Défini")</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D17" s="40" t="n">
+      <x:c r="D17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$19,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="40" t="n">
+      <x:c r="E17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$19,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F17" s="40" t="n">
+      <x:c r="F17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$19,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="40" t="n">
+      <x:c r="G17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$19,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H17" s="40" t="n">
+      <x:c r="H17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$19,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I17" s="40" t="n">
+      <x:c r="I17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$19,"Extrapolation")</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="J17" s="40" t="n">
+      <x:c r="J17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$19,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="40" t="n">
+      <x:c r="K17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$19,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="40" t="n">
+      <x:c r="L17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$19,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="40" t="n">
+      <x:c r="M17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$E$7:$E$19,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="35" t="str">
+      <x:c r="A18" s="33" t="str">
         <x:v>Ennemis et boss</x:v>
       </x:c>
-      <x:c r="B18" s="39" t="n">
+      <x:c r="B18" s="37" t="n">
         <x:f>COUNTA('Ennemis_boss'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C18" s="39" t="n">
+      <x:c r="C18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D18" s="39" t="n">
+      <x:c r="D18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="39" t="n">
+      <x:c r="E18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="39" t="n">
+      <x:c r="F18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="39" t="n">
+      <x:c r="G18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H18" s="39" t="n">
+      <x:c r="H18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I18" s="39" t="n">
+      <x:c r="I18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J18" s="39" t="n">
+      <x:c r="J18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="39" t="n">
+      <x:c r="K18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="39" t="n">
+      <x:c r="L18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="39" t="n">
+      <x:c r="M18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2756,104 +2750,104 @@
       <x:c r="A19" s="2" t="str">
         <x:v>Missions</x:v>
       </x:c>
-      <x:c r="B19" s="40" t="n">
+      <x:c r="B19" s="38" t="n">
         <x:f>COUNTA('Missions'!$A$7:$A$19)</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C19" s="40" t="n">
+      <x:c r="C19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$19,"Défini")</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D19" s="40" t="n">
+      <x:c r="D19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$19,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E19" s="40" t="n">
+      <x:c r="E19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$19,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="40" t="n">
+      <x:c r="F19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$19,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="40" t="n">
+      <x:c r="G19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$19,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H19" s="40" t="n">
+      <x:c r="H19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$19,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I19" s="40" t="n">
+      <x:c r="I19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$19,"Extrapolation")</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="J19" s="40" t="n">
+      <x:c r="J19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$19,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="40" t="n">
+      <x:c r="K19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$19,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="40" t="n">
+      <x:c r="L19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$19,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M19" s="40" t="n">
+      <x:c r="M19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$E$7:$E$19,"P0")</x:f>
         <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="35" t="str">
+      <x:c r="A20" s="33" t="str">
         <x:v>Secondaires et DLC</x:v>
       </x:c>
-      <x:c r="B20" s="39" t="n">
+      <x:c r="B20" s="37" t="n">
         <x:f>COUNTA('Secondaires_DLC'!$A$7:$A$19)</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C20" s="39" t="n">
+      <x:c r="C20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$19,"Défini")</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D20" s="39" t="n">
+      <x:c r="D20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$19,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E20" s="39" t="n">
+      <x:c r="E20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$19,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F20" s="39" t="n">
+      <x:c r="F20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$19,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G20" s="39" t="n">
+      <x:c r="G20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$19,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H20" s="39" t="n">
+      <x:c r="H20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$19,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I20" s="39" t="n">
+      <x:c r="I20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$19,"Extrapolation")</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="J20" s="39" t="n">
+      <x:c r="J20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$19,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K20" s="39" t="n">
+      <x:c r="K20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$19,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L20" s="39" t="n">
+      <x:c r="L20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$19,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="39" t="n">
+      <x:c r="M20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$E$7:$E$19,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2862,104 +2856,104 @@
       <x:c r="A21" s="2" t="str">
         <x:v>Choix et relations</x:v>
       </x:c>
-      <x:c r="B21" s="40" t="n">
+      <x:c r="B21" s="38" t="n">
         <x:f>COUNTA('Choix_relations'!$A$7:$A$19)</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C21" s="40" t="n">
+      <x:c r="C21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$19,"Défini")</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D21" s="40" t="n">
+      <x:c r="D21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$19,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E21" s="40" t="n">
+      <x:c r="E21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$19,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="40" t="n">
+      <x:c r="F21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$19,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G21" s="40" t="n">
+      <x:c r="G21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$19,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H21" s="40" t="n">
+      <x:c r="H21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$19,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I21" s="40" t="n">
+      <x:c r="I21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$19,"Extrapolation")</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="J21" s="40" t="n">
+      <x:c r="J21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$19,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K21" s="40" t="n">
+      <x:c r="K21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$19,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="40" t="n">
+      <x:c r="L21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$19,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M21" s="40" t="n">
+      <x:c r="M21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$E$7:$E$19,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="35" t="str">
+      <x:c r="A22" s="33" t="str">
         <x:v>Dialogues</x:v>
       </x:c>
-      <x:c r="B22" s="39" t="n">
+      <x:c r="B22" s="37" t="n">
         <x:f>COUNTA('Dialogues'!$A$7:$A$19)</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C22" s="39" t="n">
+      <x:c r="C22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$19,"Défini")</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D22" s="39" t="n">
+      <x:c r="D22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$19,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E22" s="39" t="n">
+      <x:c r="E22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$19,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F22" s="39" t="n">
+      <x:c r="F22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$19,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G22" s="39" t="n">
+      <x:c r="G22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$19,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="39" t="n">
+      <x:c r="H22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$19,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I22" s="39" t="n">
+      <x:c r="I22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$19,"Extrapolation")</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="J22" s="39" t="n">
+      <x:c r="J22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$19,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="39" t="n">
+      <x:c r="K22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$19,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="39" t="n">
+      <x:c r="L22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$19,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="39" t="n">
+      <x:c r="M22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$E$7:$E$19,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2968,104 +2962,104 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Cinématiques</x:v>
       </x:c>
-      <x:c r="B23" s="40" t="n">
+      <x:c r="B23" s="38" t="n">
         <x:f>COUNTA('Cinematiques'!$A$7:$A$19)</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C23" s="40" t="n">
+      <x:c r="C23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$19,"Défini")</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D23" s="40" t="n">
+      <x:c r="D23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$19,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="40" t="n">
+      <x:c r="E23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$19,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F23" s="40" t="n">
+      <x:c r="F23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$19,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="40" t="n">
+      <x:c r="G23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$19,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H23" s="40" t="n">
+      <x:c r="H23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$19,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I23" s="40" t="n">
+      <x:c r="I23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$19,"Extrapolation")</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="J23" s="40" t="n">
+      <x:c r="J23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$19,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K23" s="40" t="n">
+      <x:c r="K23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$19,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="40" t="n">
+      <x:c r="L23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$19,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M23" s="40" t="n">
+      <x:c r="M23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$E$7:$E$19,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="35" t="str">
+      <x:c r="A24" s="33" t="str">
         <x:v>Armes</x:v>
       </x:c>
-      <x:c r="B24" s="39" t="n">
+      <x:c r="B24" s="37" t="n">
         <x:f>COUNTA('Armes'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C24" s="39" t="n">
+      <x:c r="C24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D24" s="39" t="n">
+      <x:c r="D24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E24" s="39" t="n">
+      <x:c r="E24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F24" s="39" t="n">
+      <x:c r="F24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="39" t="n">
+      <x:c r="G24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H24" s="39" t="n">
+      <x:c r="H24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I24" s="39" t="n">
+      <x:c r="I24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J24" s="39" t="n">
+      <x:c r="J24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="39" t="n">
+      <x:c r="K24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="39" t="n">
+      <x:c r="L24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="39" t="n">
+      <x:c r="M24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3074,104 +3068,104 @@
       <x:c r="A25" s="2" t="str">
         <x:v>Armures et équipement</x:v>
       </x:c>
-      <x:c r="B25" s="40" t="n">
+      <x:c r="B25" s="38" t="n">
         <x:f>COUNTA('Armures_equipement'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C25" s="40" t="n">
+      <x:c r="C25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D25" s="40" t="n">
+      <x:c r="D25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E25" s="40" t="n">
+      <x:c r="E25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F25" s="40" t="n">
+      <x:c r="F25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G25" s="40" t="n">
+      <x:c r="G25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H25" s="40" t="n">
+      <x:c r="H25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I25" s="40" t="n">
+      <x:c r="I25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J25" s="40" t="n">
+      <x:c r="J25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K25" s="40" t="n">
+      <x:c r="K25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="40" t="n">
+      <x:c r="L25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="40" t="n">
+      <x:c r="M25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="35" t="str">
+      <x:c r="A26" s="33" t="str">
         <x:v>Pouvoirs</x:v>
       </x:c>
-      <x:c r="B26" s="39" t="n">
+      <x:c r="B26" s="37" t="n">
         <x:f>COUNTA('Pouvoirs'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C26" s="39" t="n">
+      <x:c r="C26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D26" s="39" t="n">
+      <x:c r="D26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E26" s="39" t="n">
+      <x:c r="E26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F26" s="39" t="n">
+      <x:c r="F26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G26" s="39" t="n">
+      <x:c r="G26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H26" s="39" t="n">
+      <x:c r="H26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I26" s="39" t="n">
+      <x:c r="I26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J26" s="39" t="n">
+      <x:c r="J26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K26" s="39" t="n">
+      <x:c r="K26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="39" t="n">
+      <x:c r="L26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M26" s="39" t="n">
+      <x:c r="M26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3180,104 +3174,104 @@
       <x:c r="A27" s="2" t="str">
         <x:v>Movesets alliés</x:v>
       </x:c>
-      <x:c r="B27" s="40" t="n">
+      <x:c r="B27" s="38" t="n">
         <x:f>COUNTA('Movesets_allies'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C27" s="40" t="n">
+      <x:c r="C27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D27" s="40" t="n">
+      <x:c r="D27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E27" s="40" t="n">
+      <x:c r="E27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F27" s="40" t="n">
+      <x:c r="F27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="40" t="n">
+      <x:c r="G27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H27" s="40" t="n">
+      <x:c r="H27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I27" s="40" t="n">
+      <x:c r="I27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J27" s="40" t="n">
+      <x:c r="J27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="40" t="n">
+      <x:c r="K27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L27" s="40" t="n">
+      <x:c r="L27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="40" t="n">
+      <x:c r="M27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="35" t="str">
+      <x:c r="A28" s="33" t="str">
         <x:v>Movesets ennemis</x:v>
       </x:c>
-      <x:c r="B28" s="39" t="n">
+      <x:c r="B28" s="37" t="n">
         <x:f>COUNTA('Movesets_ennemis'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C28" s="39" t="n">
+      <x:c r="C28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D28" s="39" t="n">
+      <x:c r="D28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E28" s="39" t="n">
+      <x:c r="E28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F28" s="39" t="n">
+      <x:c r="F28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G28" s="39" t="n">
+      <x:c r="G28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="39" t="n">
+      <x:c r="H28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I28" s="39" t="n">
+      <x:c r="I28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J28" s="39" t="n">
+      <x:c r="J28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="39" t="n">
+      <x:c r="K28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="39" t="n">
+      <x:c r="L28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="39" t="n">
+      <x:c r="M28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3286,104 +3280,104 @@
       <x:c r="A29" s="2" t="str">
         <x:v>Animations</x:v>
       </x:c>
-      <x:c r="B29" s="40" t="n">
+      <x:c r="B29" s="38" t="n">
         <x:f>COUNTA('Animations'!$A$7:$A$24)</x:f>
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C29" s="40" t="n">
+      <x:c r="C29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$24,"Défini")</x:f>
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D29" s="40" t="n">
+      <x:c r="D29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$24,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E29" s="40" t="n">
+      <x:c r="E29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$24,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="40" t="n">
+      <x:c r="F29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$24,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="40" t="n">
+      <x:c r="G29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$24,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="40" t="n">
+      <x:c r="H29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$24,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I29" s="40" t="n">
+      <x:c r="I29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$24,"Extrapolation")</x:f>
         <x:v>18</x:v>
       </x:c>
-      <x:c r="J29" s="40" t="n">
+      <x:c r="J29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$24,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="40" t="n">
+      <x:c r="K29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$24,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L29" s="40" t="n">
+      <x:c r="L29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$24,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="40" t="n">
+      <x:c r="M29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$E$7:$E$24,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="35" t="str">
+      <x:c r="A30" s="33" t="str">
         <x:v>Sprites</x:v>
       </x:c>
-      <x:c r="B30" s="39" t="n">
+      <x:c r="B30" s="37" t="n">
         <x:f>COUNTA('Sprites'!$A$7:$A$24)</x:f>
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C30" s="39" t="n">
+      <x:c r="C30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$24,"Défini")</x:f>
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D30" s="39" t="n">
+      <x:c r="D30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$24,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E30" s="39" t="n">
+      <x:c r="E30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$24,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F30" s="39" t="n">
+      <x:c r="F30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$24,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G30" s="39" t="n">
+      <x:c r="G30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$24,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="39" t="n">
+      <x:c r="H30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$24,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I30" s="39" t="n">
+      <x:c r="I30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$24,"Extrapolation")</x:f>
         <x:v>18</x:v>
       </x:c>
-      <x:c r="J30" s="39" t="n">
+      <x:c r="J30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$24,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K30" s="39" t="n">
+      <x:c r="K30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$24,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L30" s="39" t="n">
+      <x:c r="L30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$24,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M30" s="39" t="n">
+      <x:c r="M30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$E$7:$E$24,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3392,104 +3386,104 @@
       <x:c r="A31" s="2" t="str">
         <x:v>VFX</x:v>
       </x:c>
-      <x:c r="B31" s="40" t="n">
+      <x:c r="B31" s="38" t="n">
         <x:f>COUNTA('VFX'!$A$7:$A$19)</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C31" s="40" t="n">
+      <x:c r="C31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$19,"Défini")</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D31" s="40" t="n">
+      <x:c r="D31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$19,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E31" s="40" t="n">
+      <x:c r="E31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$19,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F31" s="40" t="n">
+      <x:c r="F31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$19,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G31" s="40" t="n">
+      <x:c r="G31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$19,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H31" s="40" t="n">
+      <x:c r="H31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$19,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I31" s="40" t="n">
+      <x:c r="I31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$19,"Extrapolation")</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="J31" s="40" t="n">
+      <x:c r="J31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$19,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K31" s="40" t="n">
+      <x:c r="K31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$19,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L31" s="40" t="n">
+      <x:c r="L31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$19,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M31" s="40" t="n">
+      <x:c r="M31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$E$7:$E$19,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="35" t="str">
+      <x:c r="A32" s="33" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="B32" s="39" t="n">
+      <x:c r="B32" s="37" t="n">
         <x:f>COUNTA('Audio'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C32" s="39" t="n">
+      <x:c r="C32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D32" s="39" t="n">
+      <x:c r="D32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E32" s="39" t="n">
+      <x:c r="E32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F32" s="39" t="n">
+      <x:c r="F32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="39" t="n">
+      <x:c r="G32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$13,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H32" s="39" t="n">
+      <x:c r="H32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I32" s="39" t="n">
+      <x:c r="I32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="J32" s="39" t="n">
+      <x:c r="J32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="39" t="n">
+      <x:c r="K32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L32" s="39" t="n">
+      <x:c r="L32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" s="39" t="n">
+      <x:c r="M32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$E$7:$E$13,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3498,104 +3492,104 @@
       <x:c r="A33" s="2" t="str">
         <x:v>Systèmes et UI</x:v>
       </x:c>
-      <x:c r="B33" s="40" t="n">
+      <x:c r="B33" s="38" t="n">
         <x:f>COUNTA('UI_systemes'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C33" s="40" t="n">
+      <x:c r="C33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D33" s="40" t="n">
+      <x:c r="D33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E33" s="40" t="n">
+      <x:c r="E33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F33" s="40" t="n">
+      <x:c r="F33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G33" s="40" t="n">
+      <x:c r="G33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H33" s="40" t="n">
+      <x:c r="H33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I33" s="40" t="n">
+      <x:c r="I33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J33" s="40" t="n">
+      <x:c r="J33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="40" t="n">
+      <x:c r="K33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L33" s="40" t="n">
+      <x:c r="L33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M33" s="40" t="n">
+      <x:c r="M33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
-      <x:c r="A34" s="35" t="str">
+      <x:c r="A34" s="33" t="str">
         <x:v>QA</x:v>
       </x:c>
-      <x:c r="B34" s="39" t="n">
+      <x:c r="B34" s="37" t="n">
         <x:f>COUNTA('QA'!$A$7:$A$22)</x:f>
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C34" s="39" t="n">
+      <x:c r="C34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$22,"Défini")</x:f>
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D34" s="39" t="n">
+      <x:c r="D34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$22,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E34" s="39" t="n">
+      <x:c r="E34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$22,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F34" s="39" t="n">
+      <x:c r="F34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$22,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="39" t="n">
+      <x:c r="G34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$22,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="39" t="n">
+      <x:c r="H34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$22,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I34" s="39" t="n">
+      <x:c r="I34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$22,"Extrapolation")</x:f>
         <x:v>16</x:v>
       </x:c>
-      <x:c r="J34" s="39" t="n">
+      <x:c r="J34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$22,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K34" s="39" t="n">
+      <x:c r="K34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$22,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L34" s="39" t="n">
+      <x:c r="L34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$22,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M34" s="39" t="n">
+      <x:c r="M34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$E$7:$E$22,"P0")</x:f>
         <x:v>16</x:v>
       </x:c>
@@ -3604,119 +3598,119 @@
       <x:c r="A35" s="2" t="str">
         <x:v>Continuité</x:v>
       </x:c>
-      <x:c r="B35" s="40" t="n">
+      <x:c r="B35" s="38" t="n">
         <x:f>COUNTA('Continuite'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C35" s="40" t="n">
+      <x:c r="C35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D35" s="40" t="n">
+      <x:c r="D35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E35" s="40" t="n">
+      <x:c r="E35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F35" s="40" t="n">
+      <x:c r="F35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G35" s="40" t="n">
+      <x:c r="G35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H35" s="40" t="n">
+      <x:c r="H35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I35" s="40" t="n">
+      <x:c r="I35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J35" s="40" t="n">
+      <x:c r="J35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K35" s="40" t="n">
+      <x:c r="K35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L35" s="40" t="n">
+      <x:c r="L35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M35" s="40" t="n">
+      <x:c r="M35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="2"/>
-      <x:c r="B36" s="40"/>
-      <x:c r="C36" s="40"/>
-      <x:c r="D36" s="40"/>
-      <x:c r="E36" s="40"/>
-      <x:c r="F36" s="40"/>
-      <x:c r="G36" s="40"/>
-      <x:c r="H36" s="40"/>
-      <x:c r="I36" s="40"/>
-      <x:c r="J36" s="40"/>
-      <x:c r="K36" s="40"/>
-      <x:c r="L36" s="40"/>
-      <x:c r="M36" s="40"/>
+      <x:c r="B36" s="38"/>
+      <x:c r="C36" s="38"/>
+      <x:c r="D36" s="38"/>
+      <x:c r="E36" s="38"/>
+      <x:c r="F36" s="38"/>
+      <x:c r="G36" s="38"/>
+      <x:c r="H36" s="38"/>
+      <x:c r="I36" s="38"/>
+      <x:c r="J36" s="38"/>
+      <x:c r="K36" s="38"/>
+      <x:c r="L36" s="38"/>
+      <x:c r="M36" s="38"/>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="23" t="str">
+      <x:c r="A37" s="21" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B37" s="41" t="n">
+      <x:c r="B37" s="39" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>249</x:v>
       </x:c>
-      <x:c r="C37" s="41" t="n">
+      <x:c r="C37" s="39" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="D37" s="41" t="n">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D37" s="39" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E37" s="41" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E37" s="39" t="n">
         <x:f>SUM(E10:E35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F37" s="41" t="n">
+      <x:c r="F37" s="39" t="n">
         <x:f>SUM(F10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G37" s="41" t="n">
+      <x:c r="G37" s="39" t="n">
         <x:f>SUM(G10:G35)</x:f>
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H37" s="41" t="n">
+      <x:c r="H37" s="39" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>28</x:v>
       </x:c>
-      <x:c r="I37" s="41" t="n">
+      <x:c r="I37" s="39" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>202</x:v>
       </x:c>
-      <x:c r="J37" s="41" t="n">
+      <x:c r="J37" s="39" t="n">
         <x:f>SUM(J10:J35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K37" s="41" t="n">
+      <x:c r="K37" s="39" t="n">
         <x:f>SUM(K10:K35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L37" s="41" t="n">
+      <x:c r="L37" s="39" t="n">
         <x:f>SUM(L10:L35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M37" s="41" t="n">
+      <x:c r="M37" s="39" t="n">
         <x:f>SUM(M10:M35)</x:f>
         <x:v>35</x:v>
       </x:c>
@@ -3940,61 +3934,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4046,8 +4040,8 @@
         <x:v>Mass Effect: Foundation, série concernée</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4101,10 +4095,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>FOU-S-ISSUE6</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Foundation_6</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4158,10 +4152,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>FOU-S-ISSUE13</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Foundation_13</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4215,10 +4209,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>FOU-S-ISSUE9</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Foundation_9</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4254,7 +4248,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5b3faa4fd224cf3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R421b9a9361524ecd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4394,61 +4388,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4502,8 +4496,8 @@
         <x:v>Conception originale rattachée à Foundation #1</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -4555,8 +4549,8 @@
         <x:v>Conception originale rattachée à Foundation #2</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -4608,8 +4602,8 @@
         <x:v>Conception originale rattachée à Foundation #3</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -4661,8 +4655,8 @@
         <x:v>Conception originale rattachée à Foundation #4</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -4714,8 +4708,8 @@
         <x:v>Conception originale rattachée à Foundation #5</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -4767,8 +4761,8 @@
         <x:v>Conception originale rattachée à Foundation #6</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="82" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -4820,8 +4814,8 @@
         <x:v>Conception originale rattachée à Foundation #7; sujet corroboré par le volume 2</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="82" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -4873,8 +4867,8 @@
         <x:v>Conception originale rattachée à Foundation #8</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="82" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -4926,8 +4920,8 @@
         <x:v>Conception originale rattachée à Foundation #9</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="82" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -4979,8 +4973,8 @@
         <x:v>Conception originale rattachée à Foundation #10; sujet corroboré par le volume 3</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="82" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -5032,8 +5026,8 @@
         <x:v>Conception originale rattachée à Foundation #11; recouper avec VOL3</x:v>
       </x:c>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="82" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -5085,8 +5079,8 @@
         <x:v>Conception originale rattachée à Foundation #12</x:v>
       </x:c>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
     <x:row r="19" ht="82" customHeight="1">
       <x:c r="A19" s="18" t="str">
@@ -5138,8 +5132,8 @@
         <x:v>Conception originale rattachée à Foundation #13</x:v>
       </x:c>
       <x:c r="Q19" s="9" t="str"/>
-      <x:c r="R19" s="20" t="str"/>
-      <x:c r="S19" s="20" t="str"/>
+      <x:c r="R19" s="9" t="str"/>
+      <x:c r="S19" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D19">
@@ -5173,7 +5167,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78136a6ecafb4b77"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R133c20e6c6ec447e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5313,61 +5307,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5421,8 +5415,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5474,8 +5468,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5527,8 +5521,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5580,8 +5574,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5633,8 +5627,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -5686,8 +5680,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="82" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -5739,8 +5733,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="82" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -5792,8 +5786,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="82" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -5845,8 +5839,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="82" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -5898,8 +5892,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="82" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -5951,8 +5945,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="82" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -6004,8 +5998,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
     <x:row r="19" ht="82" customHeight="1">
       <x:c r="A19" s="18" t="str">
@@ -6057,8 +6051,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q19" s="9" t="str"/>
-      <x:c r="R19" s="20" t="str"/>
-      <x:c r="S19" s="20" t="str"/>
+      <x:c r="R19" s="9" t="str"/>
+      <x:c r="S19" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D19">
@@ -6092,7 +6086,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R519457f7a6214931"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4ed466e5f2d459c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6232,61 +6226,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6340,8 +6334,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -6393,8 +6387,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -6446,8 +6440,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -6499,8 +6493,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -6552,8 +6546,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -6605,8 +6599,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="82" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -6658,8 +6652,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="82" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -6711,8 +6705,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="82" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -6764,8 +6758,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="82" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -6817,8 +6811,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="82" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -6870,8 +6864,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="82" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -6923,8 +6917,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
     <x:row r="19" ht="82" customHeight="1">
       <x:c r="A19" s="18" t="str">
@@ -6976,8 +6970,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q19" s="9" t="str"/>
-      <x:c r="R19" s="20" t="str"/>
-      <x:c r="S19" s="20" t="str"/>
+      <x:c r="R19" s="9" t="str"/>
+      <x:c r="S19" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D19">
@@ -7011,7 +7005,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R935dacd60ced4273"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2fb003f2c634c26"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7151,61 +7145,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7259,8 +7253,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -7312,8 +7306,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -7365,8 +7359,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -7418,8 +7412,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -7471,8 +7465,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -7524,8 +7518,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="82" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -7577,8 +7571,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="82" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -7630,8 +7624,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="82" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -7683,8 +7677,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="82" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -7736,8 +7730,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="82" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -7789,8 +7783,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="82" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -7842,8 +7836,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
     <x:row r="19" ht="82" customHeight="1">
       <x:c r="A19" s="18" t="str">
@@ -7895,8 +7889,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q19" s="9" t="str"/>
-      <x:c r="R19" s="20" t="str"/>
-      <x:c r="S19" s="20" t="str"/>
+      <x:c r="R19" s="9" t="str"/>
+      <x:c r="S19" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D19">
@@ -7930,7 +7924,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbfb7dfc6a738485d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd464b4e2d25e4142"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8070,61 +8064,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8176,8 +8170,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8227,8 +8221,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -8278,8 +8272,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -8329,8 +8323,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -8380,8 +8374,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -8431,8 +8425,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="82" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -8482,8 +8476,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="82" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -8533,8 +8527,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="82" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -8584,8 +8578,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="82" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -8635,8 +8629,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="82" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -8686,8 +8680,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="82" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -8737,8 +8731,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
     <x:row r="19" ht="82" customHeight="1">
       <x:c r="A19" s="18" t="str">
@@ -8788,8 +8782,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q19" s="9" t="str"/>
-      <x:c r="R19" s="20" t="str"/>
-      <x:c r="S19" s="20" t="str"/>
+      <x:c r="R19" s="9" t="str"/>
+      <x:c r="S19" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D19">
@@ -8823,7 +8817,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3743d87c7947430e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R637a61f3170c4267"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8963,61 +8957,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9069,8 +9063,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9120,8 +9114,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -9155,7 +9149,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05c5b15b427e4865"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64e22bae6109410e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9295,61 +9289,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9401,8 +9395,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9452,8 +9446,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -9503,8 +9497,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -9538,7 +9532,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e550831cbac4da8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa93c666f67a4acf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9678,61 +9672,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9784,8 +9778,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -9819,7 +9813,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02e5484c8f134e33"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e955bf0afee43ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9959,61 +9953,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10067,8 +10061,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10120,8 +10114,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10173,8 +10167,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10226,8 +10220,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10279,8 +10273,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -10332,8 +10326,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="82" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -10385,8 +10379,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="82" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -10438,8 +10432,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="82" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -10491,8 +10485,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="82" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -10544,8 +10538,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D16">
@@ -10579,7 +10573,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96ca7fb4fd654159"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21b00d88404046ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10719,61 +10713,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10827,10 +10821,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>FOU-S-VOL1</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/246024/mass-effect-foundation-volume-1-by-mac-walters-various-artists/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -10884,10 +10878,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>FOU-S-VOL1</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/246024/mass-effect-foundation-volume-1-by-mac-walters-various-artists/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -10941,10 +10935,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>FOU-S-VOL1</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/246024/mass-effect-foundation-volume-1-by-mac-walters-various-artists/</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -10998,10 +10992,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>FOU-S-VOL1</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/246024/mass-effect-foundation-volume-1-by-mac-walters-various-artists/</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -11055,10 +11049,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>FOU-S-VOL2</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/240011/mass-effect-foundation-volume-2-by-mac-walters/</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -11112,10 +11106,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>FOU-S-VOL2</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/240011/mass-effect-foundation-volume-2-by-mac-walters/</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -11169,10 +11163,10 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>FOU-S-VOL2</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/240011/mass-effect-foundation-volume-2-by-mac-walters/</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="S13" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -11226,10 +11220,10 @@
       <x:c r="Q14" s="7" t="str">
         <x:v>FOU-S-VOL2</x:v>
       </x:c>
-      <x:c r="R14" s="21" t="str">
+      <x:c r="R14" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/240011/mass-effect-foundation-volume-2-by-mac-walters/</x:v>
       </x:c>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="S14" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -11283,10 +11277,10 @@
       <x:c r="Q15" s="9" t="str">
         <x:v>FOU-S-VOL3</x:v>
       </x:c>
-      <x:c r="R15" s="20" t="str">
+      <x:c r="R15" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/243699/mass-effect-foundation-volume-3-by-mac-walters-and-tony-parker/9781621159056/</x:v>
       </x:c>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="S15" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -11340,10 +11334,10 @@
       <x:c r="Q16" s="7" t="str">
         <x:v>FOU-S-VOL3</x:v>
       </x:c>
-      <x:c r="R16" s="21" t="str">
+      <x:c r="R16" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/243699/mass-effect-foundation-volume-3-by-mac-walters-and-tony-parker/9781621159056/</x:v>
       </x:c>
-      <x:c r="S16" s="21" t="str">
+      <x:c r="S16" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -11397,10 +11391,10 @@
       <x:c r="Q17" s="9" t="str">
         <x:v>FOU-S-VOL3</x:v>
       </x:c>
-      <x:c r="R17" s="20" t="str">
+      <x:c r="R17" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/243699/mass-effect-foundation-volume-3-by-mac-walters-and-tony-parker/9781621159056/</x:v>
       </x:c>
-      <x:c r="S17" s="20" t="str">
+      <x:c r="S17" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -11436,7 +11430,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fa6279faff94078"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc5d3d528d8a4417"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11576,61 +11570,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11684,8 +11678,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11737,8 +11731,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11790,8 +11784,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11843,8 +11837,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -11896,8 +11890,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -11949,8 +11943,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="82" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -12002,8 +11996,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="82" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -12055,8 +12049,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -12090,7 +12084,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ee1116ca6d740b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61225743b3d8438f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12230,61 +12224,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12336,8 +12330,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12387,8 +12381,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12438,8 +12432,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12489,8 +12483,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12540,8 +12534,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -12591,8 +12585,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="82" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -12642,8 +12636,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="82" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -12693,8 +12687,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="82" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -12744,8 +12738,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="82" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -12795,8 +12789,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="82" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -12846,8 +12840,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="82" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -12897,8 +12891,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
     <x:row r="19" ht="82" customHeight="1">
       <x:c r="A19" s="18" t="str">
@@ -12948,8 +12942,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q19" s="9" t="str"/>
-      <x:c r="R19" s="20" t="str"/>
-      <x:c r="S19" s="20" t="str"/>
+      <x:c r="R19" s="9" t="str"/>
+      <x:c r="S19" s="9" t="str"/>
     </x:row>
     <x:row r="20" ht="82" customHeight="1">
       <x:c r="A20" s="19" t="str">
@@ -12999,8 +12993,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q20" s="7" t="str"/>
-      <x:c r="R20" s="21" t="str"/>
-      <x:c r="S20" s="21" t="str"/>
+      <x:c r="R20" s="7" t="str"/>
+      <x:c r="S20" s="7" t="str"/>
     </x:row>
     <x:row r="21" ht="82" customHeight="1">
       <x:c r="A21" s="18" t="str">
@@ -13050,8 +13044,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q21" s="9" t="str"/>
-      <x:c r="R21" s="20" t="str"/>
-      <x:c r="S21" s="20" t="str"/>
+      <x:c r="R21" s="9" t="str"/>
+      <x:c r="S21" s="9" t="str"/>
     </x:row>
     <x:row r="22" ht="82" customHeight="1">
       <x:c r="A22" s="19" t="str">
@@ -13101,8 +13095,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q22" s="7" t="str"/>
-      <x:c r="R22" s="21" t="str"/>
-      <x:c r="S22" s="21" t="str"/>
+      <x:c r="R22" s="7" t="str"/>
+      <x:c r="S22" s="7" t="str"/>
     </x:row>
     <x:row r="23" ht="82" customHeight="1">
       <x:c r="A23" s="18" t="str">
@@ -13152,8 +13146,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q23" s="9" t="str"/>
-      <x:c r="R23" s="20" t="str"/>
-      <x:c r="S23" s="20" t="str"/>
+      <x:c r="R23" s="9" t="str"/>
+      <x:c r="S23" s="9" t="str"/>
     </x:row>
     <x:row r="24" ht="82" customHeight="1">
       <x:c r="A24" s="19" t="str">
@@ -13203,8 +13197,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q24" s="7" t="str"/>
-      <x:c r="R24" s="21" t="str"/>
-      <x:c r="S24" s="21" t="str"/>
+      <x:c r="R24" s="7" t="str"/>
+      <x:c r="S24" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D24">
@@ -13238,7 +13232,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1d915088e9749c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R953c4cf005c2477b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13378,61 +13372,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13482,8 +13476,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -13531,8 +13525,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -13580,8 +13574,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -13629,8 +13623,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -13678,8 +13672,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -13727,8 +13721,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="82" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -13776,8 +13770,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="82" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -13825,8 +13819,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="82" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -13874,8 +13868,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="82" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -13923,8 +13917,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="82" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -13972,8 +13966,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="82" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -14021,8 +14015,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
     <x:row r="19" ht="82" customHeight="1">
       <x:c r="A19" s="18" t="str">
@@ -14070,8 +14064,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q19" s="9" t="str"/>
-      <x:c r="R19" s="20" t="str"/>
-      <x:c r="S19" s="20" t="str"/>
+      <x:c r="R19" s="9" t="str"/>
+      <x:c r="S19" s="9" t="str"/>
     </x:row>
     <x:row r="20" ht="82" customHeight="1">
       <x:c r="A20" s="19" t="str">
@@ -14119,8 +14113,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q20" s="7" t="str"/>
-      <x:c r="R20" s="21" t="str"/>
-      <x:c r="S20" s="21" t="str"/>
+      <x:c r="R20" s="7" t="str"/>
+      <x:c r="S20" s="7" t="str"/>
     </x:row>
     <x:row r="21" ht="82" customHeight="1">
       <x:c r="A21" s="18" t="str">
@@ -14168,8 +14162,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q21" s="9" t="str"/>
-      <x:c r="R21" s="20" t="str"/>
-      <x:c r="S21" s="20" t="str"/>
+      <x:c r="R21" s="9" t="str"/>
+      <x:c r="S21" s="9" t="str"/>
     </x:row>
     <x:row r="22" ht="82" customHeight="1">
       <x:c r="A22" s="19" t="str">
@@ -14217,8 +14211,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q22" s="7" t="str"/>
-      <x:c r="R22" s="21" t="str"/>
-      <x:c r="S22" s="21" t="str"/>
+      <x:c r="R22" s="7" t="str"/>
+      <x:c r="S22" s="7" t="str"/>
     </x:row>
     <x:row r="23" ht="82" customHeight="1">
       <x:c r="A23" s="18" t="str">
@@ -14266,8 +14260,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q23" s="9" t="str"/>
-      <x:c r="R23" s="20" t="str"/>
-      <x:c r="S23" s="20" t="str"/>
+      <x:c r="R23" s="9" t="str"/>
+      <x:c r="S23" s="9" t="str"/>
     </x:row>
     <x:row r="24" ht="82" customHeight="1">
       <x:c r="A24" s="19" t="str">
@@ -14315,8 +14309,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q24" s="7" t="str"/>
-      <x:c r="R24" s="21" t="str"/>
-      <x:c r="S24" s="21" t="str"/>
+      <x:c r="R24" s="7" t="str"/>
+      <x:c r="S24" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D24">
@@ -14350,7 +14344,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd586cbcad1f14b2c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3f8a75e139149ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14490,61 +14484,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -14596,8 +14590,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -14647,8 +14641,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -14698,8 +14692,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -14749,8 +14743,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -14800,8 +14794,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -14851,8 +14845,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="82" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -14902,8 +14896,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="82" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -14953,8 +14947,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="82" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -15004,8 +14998,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="82" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -15055,8 +15049,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="82" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -15106,8 +15100,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="82" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -15157,8 +15151,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
     <x:row r="19" ht="82" customHeight="1">
       <x:c r="A19" s="18" t="str">
@@ -15208,8 +15202,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q19" s="9" t="str"/>
-      <x:c r="R19" s="20" t="str"/>
-      <x:c r="S19" s="20" t="str"/>
+      <x:c r="R19" s="9" t="str"/>
+      <x:c r="S19" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D19">
@@ -15243,7 +15237,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41a771c1c25a4386"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b4e355f4c84416a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15383,61 +15377,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -15491,8 +15485,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -15544,8 +15538,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -15597,8 +15591,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -15650,8 +15644,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -15703,8 +15697,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -15756,8 +15750,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="82" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -15809,8 +15803,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D13">
@@ -15844,7 +15838,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76f9f3e1b6e642aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd98211e10b2f42c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15984,61 +15978,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -16086,8 +16080,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -16133,8 +16127,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -16180,8 +16174,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -16227,8 +16221,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -16262,7 +16256,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc46d51a12e434548"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe5f767cf584483e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16402,61 +16396,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -16504,8 +16498,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -16551,8 +16545,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -16598,8 +16592,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -16645,8 +16639,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -16692,8 +16686,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -16739,8 +16733,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -16786,8 +16780,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -16833,8 +16827,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -16880,8 +16874,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -16927,8 +16921,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="68" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -16974,8 +16968,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="68" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -17021,8 +17015,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
     <x:row r="19" ht="68" customHeight="1">
       <x:c r="A19" s="18" t="str">
@@ -17068,8 +17062,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q19" s="9" t="str"/>
-      <x:c r="R19" s="20" t="str"/>
-      <x:c r="S19" s="20" t="str"/>
+      <x:c r="R19" s="9" t="str"/>
+      <x:c r="S19" s="9" t="str"/>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
       <x:c r="A20" s="19" t="str">
@@ -17113,8 +17107,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q20" s="7" t="str"/>
-      <x:c r="R20" s="21" t="str"/>
-      <x:c r="S20" s="21" t="str"/>
+      <x:c r="R20" s="7" t="str"/>
+      <x:c r="S20" s="7" t="str"/>
     </x:row>
     <x:row r="21" ht="54" customHeight="1">
       <x:c r="A21" s="18" t="str">
@@ -17158,8 +17152,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q21" s="9" t="str"/>
-      <x:c r="R21" s="20" t="str"/>
-      <x:c r="S21" s="20" t="str"/>
+      <x:c r="R21" s="9" t="str"/>
+      <x:c r="S21" s="9" t="str"/>
     </x:row>
     <x:row r="22" ht="96" customHeight="1">
       <x:c r="A22" s="19" t="str">
@@ -17203,8 +17197,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q22" s="7" t="str"/>
-      <x:c r="R22" s="21" t="str"/>
-      <x:c r="S22" s="21" t="str"/>
+      <x:c r="R22" s="7" t="str"/>
+      <x:c r="S22" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D22">
@@ -17238,7 +17232,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8cfb0f290d54c4b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc46deb7e2724ff2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17378,61 +17372,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -17478,8 +17472,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -17523,8 +17517,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -17558,7 +17552,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20a2aaf2474e43ad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8831debb5ed94c42"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17623,10 +17617,10 @@
       <x:c r="F5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Champ</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="B6" s="30" t="str">
         <x:v>Définition</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
@@ -17670,12 +17664,12 @@
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
     </x:row>
-    <x:row r="10" ht="82" customHeight="1">
+    <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="7" t="str">
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Dossier de production articulé autour des investigations de Rasa et des histoires de l’entourage de Shepard. Chaque numéro a son objectif proposé, une stratégie locale, des intentions de dialogue, un objet, un raccord visuel et une recette; le dispositif conserve les flashbacks et limites de connaissance.</x:v>
+        <x:v>249 fiches de production ; 1 fiches au stade Prototype de portée partielle. Les autres livrables restent des spécifications ; aucun achèvement intégral 1:1 revendiqué.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -17694,11 +17688,11 @@
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="d">
+      <x:c r="B12" s="42" t="d">
         <x:v>2026-10-22T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
@@ -17851,22 +17845,22 @@
       <x:c r="F25" s="2"/>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="30" t="str">
+      <x:c r="A26" s="28" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="str">
+      <x:c r="B26" s="29" t="str">
         <x:v>Titre</x:v>
       </x:c>
-      <x:c r="C26" s="31" t="str">
+      <x:c r="C26" s="29" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="str">
+      <x:c r="D26" s="29" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="E26" s="31" t="str">
+      <x:c r="E26" s="29" t="str">
         <x:v>Périmètre</x:v>
       </x:c>
-      <x:c r="F26" s="32" t="str">
+      <x:c r="F26" s="30" t="str">
         <x:v>Accès et limites</x:v>
       </x:c>
     </x:row>
@@ -18255,13 +18249,13 @@
       <x:c r="F47" s="2"/>
     </x:row>
     <x:row r="48" ht="34" customHeight="1">
-      <x:c r="A48" s="30" t="str">
+      <x:c r="A48" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B48" s="31" t="str">
+      <x:c r="B48" s="29" t="str">
         <x:v>Couverture actuelle</x:v>
       </x:c>
-      <x:c r="C48" s="32" t="str">
+      <x:c r="C48" s="30" t="str">
         <x:v>Travail restant</x:v>
       </x:c>
       <x:c r="D48" s="2"/>
@@ -18632,10 +18626,16 @@
       <x:c r="E74" s="2"/>
       <x:c r="F74" s="2"/>
     </x:row>
-    <x:row r="75" ht="22" customHeight="1">
-      <x:c r="A75" s="2"/>
-      <x:c r="B75" s="2"/>
-      <x:c r="C75" s="2"/>
+    <x:row r="75" ht="96" customHeight="1">
+      <x:c r="A75" s="6" t="str">
+        <x:v>Complément lectures contextualisées</x:v>
+      </x:c>
+      <x:c r="B75" s="6" t="str">
+        <x:v>1 références supplémentaires au stade Prototype dans 1 parcours de lecture (1 pages de paraphrases documentaires sourcées), limités à leurs segments exacts.</x:v>
+      </x:c>
+      <x:c r="C75" s="6" t="str">
+        <x:v>Les faits, références, sources et réserves d’origine sont conservés. Ces lectures ne constituent ni un découpage intégral, ni une scène jouable, ni un recrutement ; modèles, voix et animations de l’œuvre ne sont pas produits.</x:v>
+      </x:c>
       <x:c r="D75" s="2"/>
       <x:c r="E75" s="2"/>
       <x:c r="F75" s="2"/>
@@ -19191,6 +19191,14 @@
       <x:c r="D144" s="2"/>
       <x:c r="E144" s="2"/>
       <x:c r="F144" s="2"/>
+    </x:row>
+    <x:row r="145" ht="22" customHeight="1">
+      <x:c r="A145" s="2"/>
+      <x:c r="B145" s="2"/>
+      <x:c r="C145" s="2"/>
+      <x:c r="D145" s="2"/>
+      <x:c r="E145" s="2"/>
+      <x:c r="F145" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19332,61 +19340,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -19440,10 +19448,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>FOU-S-CHARS</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Characters/Mass_Effect%3A_Foundation</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -19497,10 +19505,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>FOU-S-ISSUE4</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Foundation_4</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -19554,10 +19562,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>FOU-S-ISSUE4</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Foundation_4</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -19611,10 +19619,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>FOU-S-ISSUE12</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Foundation_12</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -19668,10 +19676,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>FOU-S-ISSUE12</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Foundation_12</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -19725,10 +19733,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>FOU-S-CHARS</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Characters/Mass_Effect%3A_Foundation</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -19782,10 +19790,10 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>FOU-S-VOL3</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/243699/mass-effect-foundation-volume-3-by-mac-walters-and-tony-parker/9781621159056/</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="S13" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -19821,7 +19829,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02f163c6921640c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra08382bbbd9c4645"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19848,7 +19856,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="114" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="225" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -19961,61 +19969,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -20061,10 +20069,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>FOU-S-OMNI2</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/556082/mass-effect-omnibus-volume-2-by-jeremy-barlow/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -20110,10 +20118,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>FOU-S-VOL1</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/246024/mass-effect-foundation-volume-1-by-mac-walters-various-artists/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -20159,10 +20167,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>FOU-S-VOL2</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/240011/mass-effect-foundation-volume-2-by-mac-walters/</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -20208,10 +20216,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>FOU-S-VOL3</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/243699/mass-effect-foundation-volume-3-by-mac-walters-and-tony-parker/9781621159056/</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -20257,10 +20265,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>FOU-S-SERIES</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Foundation</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -20306,10 +20314,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>FOU-S-CHARS</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Characters/Mass_Effect%3A_Foundation</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -20355,10 +20363,10 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>FOU-S-ISSUE1</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Foundation_1</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="S13" s="9" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -20404,10 +20412,10 @@
       <x:c r="Q14" s="7" t="str">
         <x:v>FOU-S-CHARS</x:v>
       </x:c>
-      <x:c r="R14" s="21" t="str">
+      <x:c r="R14" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Characters/Mass_Effect%3A_Foundation</x:v>
       </x:c>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="S14" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -20453,10 +20461,10 @@
       <x:c r="Q15" s="9" t="str">
         <x:v>FOU-S-STORY</x:v>
       </x:c>
-      <x:c r="R15" s="20" t="str">
+      <x:c r="R15" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline</x:v>
       </x:c>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="S15" s="9" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -20502,10 +20510,10 @@
       <x:c r="Q16" s="7" t="str">
         <x:v>FOU-S-ISSUE4</x:v>
       </x:c>
-      <x:c r="R16" s="21" t="str">
+      <x:c r="R16" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Foundation_4</x:v>
       </x:c>
-      <x:c r="S16" s="21" t="str">
+      <x:c r="S16" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -20517,7 +20525,7 @@
         <x:v>#5 — recherche de Shepard</x:v>
       </x:c>
       <x:c r="C17" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D17" s="16" t="str">
         <x:v>Établi</x:v>
@@ -20536,7 +20544,7 @@
       <x:c r="J17" s="9" t="str"/>
       <x:c r="K17" s="9" t="str"/>
       <x:c r="L17" s="9" t="str">
-        <x:v>Livrable proposé : spécification FOU/lore/sc-05-ref; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Référence documentaire FOU-SC-05-REF consultable dans les lectures fou-recherche de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ni incarnation de personnage produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M17" s="9" t="str">
         <x:v>Le fil de Rasa et les souvenirs des autres personnages restent séparés. Les options d’adaptation ne réécrivent ni les décès, ni l’issue du génophage, ni les origines des équipiers; aucun personnage n’est recruté uniquement parce que son dossier est consulté.</x:v>
@@ -20551,11 +20559,11 @@
       <x:c r="Q17" s="9" t="str">
         <x:v>FOU-S-ISSUE5</x:v>
       </x:c>
-      <x:c r="R17" s="20" t="str">
+      <x:c r="R17" s="9" t="str">
         <x:v>https://books.apple.com/fr/book/mass-effect-foundation-5/id1047063498</x:v>
       </x:c>
-      <x:c r="S17" s="20" t="str">
-        <x:v>Ne remplace pas la lecture du numéro.</x:v>
+      <x:c r="S17" s="9" t="str">
+        <x:v>Ne remplace pas la lecture du numéro. Prototype limité à une paraphrase documentaire sourcée et aux références visitées ; pas de reproduction intégrale du récit. Une lecture n’accorde ni recrutement, équipement, victoire ni récompense de campagne.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="82" customHeight="1">
@@ -20600,10 +20608,10 @@
       <x:c r="Q18" s="7" t="str">
         <x:v>FOU-S-ISSUE6</x:v>
       </x:c>
-      <x:c r="R18" s="21" t="str">
+      <x:c r="R18" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Foundation_6</x:v>
       </x:c>
-      <x:c r="S18" s="21" t="str">
+      <x:c r="S18" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -20649,10 +20657,10 @@
       <x:c r="Q19" s="9" t="str">
         <x:v>FOU-S-ISSUE7</x:v>
       </x:c>
-      <x:c r="R19" s="20" t="str">
+      <x:c r="R19" s="9" t="str">
         <x:v>https://comicpreviews.com/series/mass-effect-foundation-2013</x:v>
       </x:c>
-      <x:c r="S19" s="20" t="str">
+      <x:c r="S19" s="9" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -20698,10 +20706,10 @@
       <x:c r="Q20" s="7" t="str">
         <x:v>FOU-S-ISSUE8</x:v>
       </x:c>
-      <x:c r="R20" s="21" t="str">
+      <x:c r="R20" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Foundation_8</x:v>
       </x:c>
-      <x:c r="S20" s="21" t="str">
+      <x:c r="S20" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -20747,10 +20755,10 @@
       <x:c r="Q21" s="9" t="str">
         <x:v>FOU-S-ISSUE9</x:v>
       </x:c>
-      <x:c r="R21" s="20" t="str">
+      <x:c r="R21" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Foundation_9</x:v>
       </x:c>
-      <x:c r="S21" s="20" t="str">
+      <x:c r="S21" s="9" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -20796,10 +20804,10 @@
       <x:c r="Q22" s="7" t="str">
         <x:v>FOU-S-ISSUE10</x:v>
       </x:c>
-      <x:c r="R22" s="21" t="str">
+      <x:c r="R22" s="7" t="str">
         <x:v>https://www.g-mart.com/static/f129000.html</x:v>
       </x:c>
-      <x:c r="S22" s="21" t="str">
+      <x:c r="S22" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -20845,10 +20853,10 @@
       <x:c r="Q23" s="9" t="str">
         <x:v>FOU-S-ISSUE11</x:v>
       </x:c>
-      <x:c r="R23" s="20" t="str">
+      <x:c r="R23" s="9" t="str">
         <x:v>https://comicpreviews.com/products/mass-effect-foundation-11</x:v>
       </x:c>
-      <x:c r="S23" s="20" t="str">
+      <x:c r="S23" s="9" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -20894,10 +20902,10 @@
       <x:c r="Q24" s="7" t="str">
         <x:v>FOU-S-ISSUE12</x:v>
       </x:c>
-      <x:c r="R24" s="21" t="str">
+      <x:c r="R24" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Foundation_12</x:v>
       </x:c>
-      <x:c r="S24" s="21" t="str">
+      <x:c r="S24" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -20943,10 +20951,10 @@
       <x:c r="Q25" s="9" t="str">
         <x:v>FOU-S-ISSUE13</x:v>
       </x:c>
-      <x:c r="R25" s="20" t="str">
+      <x:c r="R25" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Foundation_13</x:v>
       </x:c>
-      <x:c r="S25" s="20" t="str">
+      <x:c r="S25" s="9" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -20982,7 +20990,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49665a88573b418b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d2f90c7f27341d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21122,61 +21130,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -21224,10 +21232,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>FOU-S-ISSUE1</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Foundation_1</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -21275,10 +21283,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>FOU-S-VOL1</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/246024/mass-effect-foundation-volume-1-by-mac-walters-various-artists/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -21326,10 +21334,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>FOU-S-STORY</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -21377,10 +21385,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>FOU-S-ISSUE4</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Foundation_4</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -21428,10 +21436,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>FOU-S-VOL2</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/240011/mass-effect-foundation-volume-2-by-mac-walters/</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Les noms précis de lieux secondaires ne sont pas inventés; relever ceux de l’édition avant décor final.</x:v>
       </x:c>
     </x:row>
@@ -21479,10 +21487,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>FOU-S-ISSUE9</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Foundation_9</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -21530,10 +21538,10 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>FOU-S-ISSUE13</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Foundation_13</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="S13" s="9" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -21569,7 +21577,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref7978a59dd1434e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5f1e00919ff494d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21709,61 +21717,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -21815,8 +21823,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -21866,8 +21874,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -21917,8 +21925,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -21968,8 +21976,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -22019,8 +22027,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -22070,8 +22078,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="82" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -22121,8 +22129,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D13">
@@ -22156,7 +22164,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e3cd56e364d42df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R890b92806e694778"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22296,61 +22304,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -22400,8 +22408,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -22449,8 +22457,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -22498,8 +22506,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -22547,8 +22555,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -22596,8 +22604,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -22645,8 +22653,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="82" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -22694,8 +22702,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D13">
@@ -22729,7 +22737,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2fa6c37d4d24b9e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4a3ab70d2004cea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22869,61 +22877,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -22973,8 +22981,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -23022,8 +23030,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -23071,8 +23079,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -23120,8 +23128,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -23169,8 +23177,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -23218,8 +23226,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="82" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -23267,8 +23275,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D13">
@@ -23302,7 +23310,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4618e2f981d4b24"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91ee4025f81049c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23442,61 +23450,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -23550,8 +23558,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -23603,8 +23611,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -23656,8 +23664,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -23709,8 +23717,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -23762,8 +23770,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -23815,8 +23823,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="82" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -23868,8 +23876,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="82" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -23921,8 +23929,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="82" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -23974,8 +23982,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="82" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -24027,8 +24035,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="82" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -24080,8 +24088,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="82" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -24133,8 +24141,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
     <x:row r="19" ht="82" customHeight="1">
       <x:c r="A19" s="18" t="str">
@@ -24186,8 +24194,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q19" s="9" t="str"/>
-      <x:c r="R19" s="20" t="str"/>
-      <x:c r="S19" s="20" t="str"/>
+      <x:c r="R19" s="9" t="str"/>
+      <x:c r="S19" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D19">
@@ -24221,7 +24229,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8aa56e8cdf0e4aea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec0edd56adc546ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Foundation_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Foundation_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rc136dcc32e5846b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rf529302c862e45cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R222d8bc9bddb4bc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R07d0a0f0cdfc4130"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R32d9b303e2c9472b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R69f9c0b8db594a4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rc6018a7b23bf4c4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R3b2282aab6e244c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R7cc33257bdd04e79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R6603a0c4a6c14d9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Ra115de8061fc489d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rf5815d9f848144bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R4e9bdb83cd504e1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R71a4591ffbb843b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R56307755e3ab4858"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R253b067b437a4f97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Raae072b9431841c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rbba4400e35c34b3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R61feb57f92d64b75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R6fc1428ccf784785"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R05d19e3244a744ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rca387d016ee044b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R6ffe11a9617b4963"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rfa447d7e703542f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R7e224c8485ad4564"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R77e2252939754191"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rba1b0066d3834166"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Ra1f8e35852dc4c85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Re015b4d1e05c4598"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R928dad3c4afa4855"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R6bfe6ba5fa6740db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R071a482b3b114ca7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rf26c3538ebf74cbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Re27d0836ef3241f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rf58c9d93a3a04465"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R1be88281f4ad4684"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R4b992c10396d477c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R7069a21811904f14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rcdf9d77fbc534306"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R7554e1189b95461f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R56583ad0f7d14bbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rd99ea9ce3b77436d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rfc98bedb3df0409a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rb2e843e6585044c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Ra868cc3ce809415c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R0498deac5600418c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rda96f53c4bb34117"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Re6ae4b409168486d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R4091dc47aab14eaa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R14e8db8c0e44469c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R774755c7bac249e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R45beb914fd8640d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rc68023775f2a4bd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rd28ad9c3dd2e4d23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R16fba5b2945747c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R36d2e0c279524026"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4248,7 +4248,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R421b9a9361524ecd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49e842a6a21d4e95"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5167,7 +5167,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R133c20e6c6ec447e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80ecad86f9564db6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6086,7 +6086,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4ed466e5f2d459c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R055eeaecf37b433d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7005,7 +7005,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2fb003f2c634c26"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0b2ceb4abdc4b5d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7924,7 +7924,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd464b4e2d25e4142"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0be3fee562ca484f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8817,7 +8817,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R637a61f3170c4267"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c76b7f584054301"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9149,7 +9149,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64e22bae6109410e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref580ae3424641a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9532,7 +9532,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa93c666f67a4acf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7cbc3e7ca984754"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9813,7 +9813,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e955bf0afee43ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54aed8a21b7c4daa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10573,7 +10573,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21b00d88404046ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9f71ca9369347ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11430,7 +11430,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc5d3d528d8a4417"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9711439cf244e5d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12084,7 +12084,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61225743b3d8438f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6f7840e47fb4100"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13232,7 +13232,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R953c4cf005c2477b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2243846532549c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14344,7 +14344,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3f8a75e139149ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac2ca9507c5045da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15237,7 +15237,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b4e355f4c84416a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb78bab4204d40f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15838,7 +15838,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd98211e10b2f42c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64dc05cbebc04590"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16256,7 +16256,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe5f767cf584483e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79dc5d606f344e8f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17232,7 +17232,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc46deb7e2724ff2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5f06528d5d7496c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17552,7 +17552,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8831debb5ed94c42"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b172a77ab4141a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19829,7 +19829,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra08382bbbd9c4645"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d4fc3552c214ab0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20990,7 +20990,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d2f90c7f27341d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc07e93e308ef4005"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21577,7 +21577,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5f1e00919ff494d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ca9015c34fb44f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22164,7 +22164,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R890b92806e694778"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd39af6fa6d4d4aea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22737,7 +22737,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4a3ab70d2004cea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra899c61b589f4ac4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23310,7 +23310,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91ee4025f81049c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb36d5d0fdea84bf0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24229,7 +24229,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec0edd56adc546ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88ea2e0c027244ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Foundation_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Foundation_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Re015b4d1e05c4598"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R928dad3c4afa4855"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R6bfe6ba5fa6740db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R071a482b3b114ca7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rf26c3538ebf74cbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Re27d0836ef3241f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rf58c9d93a3a04465"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R1be88281f4ad4684"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R4b992c10396d477c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R7069a21811904f14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rcdf9d77fbc534306"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R7554e1189b95461f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R56583ad0f7d14bbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rd99ea9ce3b77436d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rfc98bedb3df0409a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rb2e843e6585044c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Ra868cc3ce809415c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R0498deac5600418c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rda96f53c4bb34117"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Re6ae4b409168486d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R4091dc47aab14eaa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R14e8db8c0e44469c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R774755c7bac249e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R45beb914fd8640d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rc68023775f2a4bd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rd28ad9c3dd2e4d23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R16fba5b2945747c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R36d2e0c279524026"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R37973d7ef63446c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R5eda9a147e364c5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R63a4314d7d4c4b32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rd6de0372316a40d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R6ff11eea7b61450a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R1508836beeca48d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R40446604e83449ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rfaeab45349f843b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rf2633579383648f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R8587e859552f40dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rd637e94c6d15410a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R08df01a077e64afb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R1d00108224fb40d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rfa29cf5199264f2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R3fd3a68c027e4941"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R9249516cb1f14c70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R078a12f5332c48ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rd8e1d3d40bab4bf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rafba33f8775f4b57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rac7c809658ca4e58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R6438296824304095"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rf24a7a05536f4ca5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Ra9135bd286c64c26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rc94ff94e35ef49d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R67d45aba77c742fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rfbc9714e92ff43f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R15aed60f030149bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R9c104ad2bbb540f6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4248,7 +4248,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49e842a6a21d4e95"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf35f852eb1b4587"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5167,7 +5167,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80ecad86f9564db6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdc9e9c790224746"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6086,7 +6086,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R055eeaecf37b433d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R559e41242c64442a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7005,7 +7005,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0b2ceb4abdc4b5d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cd508990cc64af0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7924,7 +7924,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0be3fee562ca484f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87d3287e2f374f2c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8817,7 +8817,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c76b7f584054301"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ceb2286184e47d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9149,7 +9149,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref580ae3424641a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ad589030b634c68"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9532,7 +9532,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7cbc3e7ca984754"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R565f851517d6486b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9813,7 +9813,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54aed8a21b7c4daa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85e80b33f7a64aab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10573,7 +10573,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9f71ca9369347ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R795050afca5a49cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11430,7 +11430,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9711439cf244e5d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44a18a64ad134df0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12084,7 +12084,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6f7840e47fb4100"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbbbb1f5f25b4b2b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13232,7 +13232,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2243846532549c4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8e842b26e1b4ba1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14344,7 +14344,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac2ca9507c5045da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44b5c48191af414f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15237,7 +15237,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb78bab4204d40f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72c2ea34f2da4699"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15838,7 +15838,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64dc05cbebc04590"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R194faac70eca4707"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16256,7 +16256,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79dc5d606f344e8f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2a6e7b4618b4e81"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17232,7 +17232,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5f06528d5d7496c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b7cdf5d7362431c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17552,7 +17552,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b172a77ab4141a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R993619390f7944d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19829,7 +19829,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d4fc3552c214ab0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0f6f87a38ac409f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20990,7 +20990,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc07e93e308ef4005"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R260c5a8158584e4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21577,7 +21577,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ca9015c34fb44f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fbcd6b9fefa486c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22164,7 +22164,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd39af6fa6d4d4aea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R886c1534a72c422f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22737,7 +22737,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra899c61b589f4ac4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb7f95abf36745cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23310,7 +23310,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb36d5d0fdea84bf0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0270a832d08b4371"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24229,7 +24229,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88ea2e0c027244ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e217a2977894cbb"/>
   </x:tableParts>
 </x:worksheet>
 </file>